--- a/forms/app/chv_quality_monitoring.xlsx
+++ b/forms/app/chv_quality_monitoring.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20387"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20389"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F9D7F8-55AA-4E1A-8F31-5BDC62017991}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C4C512-2915-4EC5-A60D-D9D20473565C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="340">
   <si>
     <t>type</t>
   </si>
@@ -660,10 +660,6 @@
     <t>r_chw_info</t>
   </si>
   <si>
-    <t>&lt;div style="text-align:center;"&gt;&lt;span&gt;**CHV name:** ${chw_name}&lt;/span&gt; 
-&lt;span&gt;**CHV ID:** ${chw_id}&lt;/span&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>r_improvement_areas_title</t>
   </si>
   <si>
@@ -946,10 +942,6 @@
     <t>Taarifa za CHV &lt;i class="fa fa-user"&gt;&lt;/i&gt;</t>
   </si>
   <si>
-    <t>&lt;div style="text-align:center;"&gt;&lt;span&gt;**Jina la CHV:** ${chw_name}&lt;/span&gt; 
-&lt;span&gt;**CHV ID:** ${chw_id}&lt;/span&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>Maeneo ya maboresho &lt;i class="fa fa-flag"&gt;&lt;/i&gt;</t>
   </si>
   <si>
@@ -1143,6 +1135,18 @@
   <si>
     <t xml:space="preserve">Je muhudumu wa afya wa kujitolea anauliza na kuchunguza jinsi mlezi anavyomkosoa mtoto? </t>
   </si>
+  <si>
+    <t>&lt;div style="text-align:center;"&gt;&lt;span&gt;**CHV name:** ${chw_name}&lt;/span&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="text-align:center;"&gt;&lt;span&gt;**Jina la CHV:** ${chw_name}&lt;/span&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>${next_follow_up_date}!='' and ${next_follow_up_date} &gt; today()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tafadhali chagua tarehe ya mbele </t>
+  </si>
 </sst>
 </file>
 
@@ -1151,7 +1155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1204,6 +1208,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1222,10 +1233,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1276,9 +1288,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4217,13 +4236,13 @@
         <v>42</v>
       </c>
       <c r="B79" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="C79" s="18" t="s">
-        <v>273</v>
-      </c>
       <c r="D79" s="18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
@@ -4253,13 +4272,13 @@
         <v>52</v>
       </c>
       <c r="B80" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C80" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="C80" s="21" t="s">
-        <v>275</v>
-      </c>
       <c r="D80" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>56</v>
@@ -4291,13 +4310,13 @@
         <v>52</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>56</v>
@@ -4329,13 +4348,13 @@
         <v>52</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>56</v>
@@ -4367,13 +4386,13 @@
         <v>52</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>56</v>
@@ -4405,13 +4424,13 @@
         <v>135</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E84" s="19"/>
       <c r="F84" s="18"/>
@@ -4441,13 +4460,13 @@
         <v>52</v>
       </c>
       <c r="B85" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C85" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="C85" s="18" t="s">
-        <v>281</v>
-      </c>
       <c r="D85" s="22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>56</v>
@@ -4479,13 +4498,13 @@
         <v>42</v>
       </c>
       <c r="B86" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C86" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="C86" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="D86" s="23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
@@ -4515,13 +4534,13 @@
         <v>52</v>
       </c>
       <c r="B87" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="C87" s="18" t="s">
-        <v>285</v>
-      </c>
       <c r="D87" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
@@ -4551,13 +4570,13 @@
         <v>52</v>
       </c>
       <c r="B88" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="C88" s="18" t="s">
-        <v>287</v>
-      </c>
       <c r="D88" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
@@ -4587,13 +4606,13 @@
         <v>52</v>
       </c>
       <c r="B89" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C89" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="C89" s="18" t="s">
-        <v>289</v>
-      </c>
       <c r="D89" s="22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
@@ -4623,13 +4642,13 @@
         <v>52</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C90" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="C90" s="18" t="s">
-        <v>291</v>
-      </c>
       <c r="D90" s="22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
@@ -4659,13 +4678,13 @@
         <v>52</v>
       </c>
       <c r="B91" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="C91" s="18" t="s">
-        <v>293</v>
-      </c>
       <c r="D91" s="22" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
@@ -4695,13 +4714,13 @@
         <v>42</v>
       </c>
       <c r="B92" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="C92" s="18" t="s">
-        <v>295</v>
-      </c>
       <c r="D92" s="23" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
@@ -4731,13 +4750,13 @@
         <v>52</v>
       </c>
       <c r="B93" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="C93" s="18" t="s">
-        <v>297</v>
-      </c>
       <c r="D93" s="19" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
@@ -4767,13 +4786,13 @@
         <v>52</v>
       </c>
       <c r="B94" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C94" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C94" s="21" t="s">
-        <v>299</v>
-      </c>
       <c r="D94" s="22" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
@@ -4803,13 +4822,13 @@
         <v>52</v>
       </c>
       <c r="B95" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C95" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="C95" s="18" t="s">
-        <v>301</v>
-      </c>
       <c r="D95" s="22" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
@@ -5682,7 +5701,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
       <c r="K120" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
@@ -5705,7 +5724,7 @@
         <v>33</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>201</v>
@@ -5720,7 +5739,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
       <c r="K121" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
@@ -5758,7 +5777,7 @@
       <c r="I122" s="8"/>
       <c r="J122" s="8"/>
       <c r="K122" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L122" s="7"/>
       <c r="M122" s="8"/>
@@ -5817,7 +5836,7 @@
         <v>205</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
@@ -5855,7 +5874,7 @@
         <v>208</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
@@ -5882,7 +5901,7 @@
       <c r="Y125" s="4"/>
       <c r="Z125" s="4"/>
     </row>
-    <row r="126" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A126" s="9" t="s">
         <v>42</v>
       </c>
@@ -5890,10 +5909,10 @@
         <v>210</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>211</v>
+        <v>336</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
@@ -5923,18 +5942,18 @@
         <v>42</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="D127" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
@@ -5961,13 +5980,13 @@
         <v>42</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D128" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -5997,18 +6016,18 @@
         <v>42</v>
       </c>
       <c r="B129" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C129" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C129" s="9" t="s">
-        <v>218</v>
-      </c>
       <c r="D129" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H129" s="10"/>
       <c r="I129" s="10"/>
@@ -6035,13 +6054,13 @@
         <v>52</v>
       </c>
       <c r="B130" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C130" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C130" s="13" t="s">
-        <v>220</v>
-      </c>
       <c r="D130" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E130" s="11" t="s">
         <v>56</v>
@@ -6070,31 +6089,33 @@
     </row>
     <row r="131" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A131" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B131" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="C131" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="D131" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I131" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="I131" s="3" t="s">
-        <v>226</v>
+      <c r="J131" s="4" t="s">
+        <v>339</v>
       </c>
-      <c r="J131" s="4"/>
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
@@ -6117,7 +6138,7 @@
         <v>33</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>201</v>
@@ -6127,14 +6148,14 @@
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
       <c r="K132" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -6152,22 +6173,22 @@
       <c r="Y132" s="4"/>
       <c r="Z132" s="4"/>
     </row>
-    <row r="133" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:26" ht="52" x14ac:dyDescent="0.6">
       <c r="A133" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="D133" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E133" s="4"/>
-      <c r="F133" s="3" t="s">
-        <v>224</v>
+      <c r="F133" s="24" t="s">
+        <v>338</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -6195,7 +6216,7 @@
         <v>33</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C134" s="9" t="s">
         <v>201</v>
@@ -6210,7 +6231,7 @@
       <c r="I134" s="10"/>
       <c r="J134" s="10"/>
       <c r="K134" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L134" s="10"/>
       <c r="M134" s="10"/>
@@ -6228,21 +6249,23 @@
       <c r="Y134" s="10"/>
       <c r="Z134" s="10"/>
     </row>
-    <row r="135" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:26" ht="52" x14ac:dyDescent="0.6">
       <c r="A135" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B135" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C135" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C135" s="13" t="s">
-        <v>234</v>
-      </c>
       <c r="D135" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E135" s="10"/>
-      <c r="F135" s="10"/>
+      <c r="F135" s="25" t="s">
+        <v>338</v>
+      </c>
       <c r="G135" s="10"/>
       <c r="H135" s="10"/>
       <c r="I135" s="10"/>
@@ -30395,7 +30418,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>1</v>
@@ -30431,142 +30454,142 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>56</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="D2" s="16" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>56</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="D5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="16" t="s">
+      <c r="C6" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>245</v>
-      </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A9" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" s="16">
         <v>0</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A10" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>250</v>
-      </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B11" s="16">
         <v>2</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>252</v>
-      </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B12" s="16">
         <v>3</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>254</v>
-      </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B13" s="16">
         <v>5</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -30574,13 +30597,13 @@
         <v>171</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="D15" s="16" t="s">
         <v>258</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
@@ -30588,13 +30611,13 @@
         <v>171</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>261</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -30615,22 +30638,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -30658,20 +30681,20 @@
         <v>161</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C2" s="17">
         <f ca="1">NOW()</f>
-        <v>44783.384753356484</v>
+        <v>44825.55971076389</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>

--- a/forms/app/chv_quality_monitoring.xlsx
+++ b/forms/app/chv_quality_monitoring.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20389"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20392"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C4C512-2915-4EC5-A60D-D9D20473565C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B8F243-655E-4F10-8A5D-FB81C5AB654E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="342">
   <si>
     <t>type</t>
   </si>
@@ -1147,6 +1147,12 @@
   <si>
     <t xml:space="preserve">Tafadhali chagua tarehe ya mbele </t>
   </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
 </sst>
 </file>
 
@@ -1155,7 +1161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1215,13 +1221,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1237,7 +1254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1294,6 +1311,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1513,7 +1532,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z996"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2085,88 +2104,88 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="3" t="s">
+    <row r="17" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A17" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+    </row>
+    <row r="18" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A18" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -2189,16 +2208,20 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -2220,13 +2243,17 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -2247,24 +2274,14 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>48</v>
-      </c>
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -2287,20 +2304,22 @@
     </row>
     <row r="23" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -2321,22 +2340,20 @@
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -2359,18 +2376,18 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>56</v>
@@ -2399,14 +2416,20 @@
     </row>
     <row r="26" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -2430,8 +2453,12 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="A27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -2458,23 +2485,13 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -2495,24 +2512,24 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A29" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>56</v>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -2533,16 +2550,22 @@
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
-    <row r="30" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="C30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -2566,8 +2589,12 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -2594,23 +2621,13 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -2633,22 +2650,22 @@
     </row>
     <row r="33" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A33" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>56</v>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -2671,14 +2688,20 @@
     </row>
     <row r="34" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A34" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="C34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -2702,8 +2725,12 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2730,23 +2757,13 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -2769,22 +2786,22 @@
     </row>
     <row r="37" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>56</v>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -2807,14 +2824,20 @@
     </row>
     <row r="38" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2838,8 +2861,12 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -2866,23 +2893,13 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2905,22 +2922,22 @@
     </row>
     <row r="41" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>56</v>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2943,14 +2960,20 @@
     </row>
     <row r="42" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A42" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="C42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2974,8 +2997,12 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3002,23 +3029,13 @@
       <c r="Z43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -3039,24 +3056,24 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>56</v>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -3079,18 +3096,20 @@
     </row>
     <row r="46" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A46" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3113,22 +3132,20 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3156,13 +3173,13 @@
         <v>52</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>56</v>
@@ -3194,13 +3211,13 @@
         <v>52</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>56</v>
@@ -3232,13 +3249,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>56</v>
@@ -3267,14 +3284,20 @@
     </row>
     <row r="51" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A51" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="C51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3298,8 +3321,12 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
+      <c r="A52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3326,23 +3353,13 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A53" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -3365,22 +3382,22 @@
     </row>
     <row r="54" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>56</v>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -3403,14 +3420,20 @@
     </row>
     <row r="55" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A55" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
+      <c r="C55" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3434,8 +3457,12 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3462,23 +3489,13 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
@@ -3499,24 +3516,24 @@
       <c r="Y57" s="4"/>
       <c r="Z57" s="4"/>
     </row>
-    <row r="58" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A58" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>56</v>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -3537,16 +3554,22 @@
       <c r="Y58" s="4"/>
       <c r="Z58" s="4"/>
     </row>
-    <row r="59" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A59" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
+      <c r="C59" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3570,8 +3593,12 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
+      <c r="A60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3598,23 +3625,13 @@
       <c r="Z60" s="4"/>
     </row>
     <row r="61" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
@@ -3635,24 +3652,24 @@
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
     </row>
-    <row r="62" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A62" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>56</v>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
@@ -3678,15 +3695,17 @@
         <v>52</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
-      <c r="E63" s="4"/>
+      <c r="E63" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -3709,15 +3728,19 @@
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
     </row>
-    <row r="64" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A64" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="C64" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
@@ -3742,8 +3765,12 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
+      <c r="A65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -3770,23 +3797,13 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A66" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
@@ -3807,24 +3824,24 @@
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
     </row>
-    <row r="67" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A67" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>56</v>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
@@ -3845,18 +3862,18 @@
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
     </row>
-    <row r="68" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A68" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>56</v>
@@ -3883,18 +3900,18 @@
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A69" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>56</v>
@@ -3926,13 +3943,13 @@
         <v>135</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>56</v>
@@ -3959,16 +3976,22 @@
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A71" s="3" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
+      <c r="C71" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -3992,8 +4015,12 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
+      <c r="A72" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -4020,23 +4047,13 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
@@ -4057,24 +4074,24 @@
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A74" s="3" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>56</v>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
@@ -4100,13 +4117,13 @@
         <v>135</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>56</v>
@@ -4133,16 +4150,22 @@
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
     </row>
-    <row r="76" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A76" s="3" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+      <c r="C76" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -4166,8 +4189,12 @@
       <c r="Z76" s="4"/>
     </row>
     <row r="77" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
+      <c r="A77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -4194,23 +4221,13 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
@@ -4231,58 +4248,58 @@
       <c r="Y78" s="4"/>
       <c r="Z78" s="4"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A79" s="11" t="s">
+    <row r="79" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+    </row>
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A80" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B80" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C80" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D80" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
-      <c r="L79" s="19"/>
-      <c r="M79" s="19"/>
-      <c r="N79" s="19"/>
-      <c r="O79" s="19"/>
-      <c r="P79" s="19"/>
-      <c r="Q79" s="19"/>
-      <c r="R79" s="19"/>
-      <c r="S79" s="19"/>
-      <c r="T79" s="19"/>
-      <c r="U79" s="19"/>
-      <c r="V79" s="19"/>
-      <c r="W79" s="19"/>
-      <c r="X79" s="19"/>
-      <c r="Y79" s="19"/>
-      <c r="Z79" s="19"/>
-    </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A80" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>56</v>
-      </c>
+      <c r="E80" s="19"/>
       <c r="F80" s="19"/>
       <c r="G80" s="19"/>
       <c r="H80" s="19"/>
@@ -4310,13 +4327,13 @@
         <v>52</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>331</v>
+        <v>274</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>56</v>
@@ -4348,13 +4365,13 @@
         <v>52</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
-      <c r="D82" s="19" t="s">
-        <v>333</v>
+      <c r="D82" s="4" t="s">
+        <v>332</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>56</v>
@@ -4386,13 +4403,13 @@
         <v>52</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>334</v>
+      <c r="D83" s="19" t="s">
+        <v>333</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>56</v>
@@ -4420,20 +4437,22 @@
       <c r="Z83" s="19"/>
     </row>
     <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A84" s="11" t="s">
-        <v>135</v>
+      <c r="A84" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
-      <c r="E84" s="19"/>
-      <c r="F84" s="18"/>
+      <c r="E84" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F84" s="19"/>
       <c r="G84" s="19"/>
       <c r="H84" s="19"/>
       <c r="I84" s="19"/>
@@ -4455,23 +4474,21 @@
       <c r="Y84" s="19"/>
       <c r="Z84" s="19"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A85" s="20" t="s">
-        <v>52</v>
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A85" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
-      <c r="C85" s="18" t="s">
-        <v>280</v>
+      <c r="C85" s="21" t="s">
+        <v>330</v>
       </c>
-      <c r="D85" s="22" t="s">
-        <v>314</v>
+      <c r="D85" s="4" t="s">
+        <v>335</v>
       </c>
-      <c r="E85" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="18"/>
       <c r="G85" s="19"/>
       <c r="H85" s="19"/>
       <c r="I85" s="19"/>
@@ -4494,19 +4511,21 @@
       <c r="Z85" s="19"/>
     </row>
     <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A86" s="11" t="s">
-        <v>42</v>
+      <c r="A86" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
-      <c r="D86" s="23" t="s">
-        <v>320</v>
+      <c r="D86" s="22" t="s">
+        <v>314</v>
       </c>
-      <c r="E86" s="19"/>
+      <c r="E86" s="19" t="s">
+        <v>56</v>
+      </c>
       <c r="F86" s="19"/>
       <c r="G86" s="19"/>
       <c r="H86" s="19"/>
@@ -4531,16 +4550,16 @@
     </row>
     <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A87" s="11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
-      <c r="D87" s="22" t="s">
-        <v>315</v>
+      <c r="D87" s="23" t="s">
+        <v>320</v>
       </c>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
@@ -4570,13 +4589,13 @@
         <v>52</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
@@ -4606,13 +4625,13 @@
         <v>52</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
@@ -4642,13 +4661,13 @@
         <v>52</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
@@ -4678,13 +4697,13 @@
         <v>52</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
@@ -4711,16 +4730,16 @@
     </row>
     <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A92" s="11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
-      <c r="D92" s="23" t="s">
-        <v>321</v>
+      <c r="D92" s="22" t="s">
+        <v>319</v>
       </c>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
@@ -4747,16 +4766,16 @@
     </row>
     <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A93" s="11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
-      <c r="D93" s="19" t="s">
-        <v>322</v>
+      <c r="D93" s="23" t="s">
+        <v>321</v>
       </c>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
@@ -4781,18 +4800,18 @@
       <c r="Y93" s="19"/>
       <c r="Z93" s="19"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A94" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
-      <c r="C94" s="21" t="s">
-        <v>298</v>
+      <c r="C94" s="18" t="s">
+        <v>296</v>
       </c>
-      <c r="D94" s="22" t="s">
-        <v>323</v>
+      <c r="D94" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
@@ -4817,18 +4836,18 @@
       <c r="Y94" s="19"/>
       <c r="Z94" s="19"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A95" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
-      <c r="C95" s="18" t="s">
-        <v>300</v>
+      <c r="C95" s="21" t="s">
+        <v>298</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
@@ -4853,41 +4872,49 @@
       <c r="Y95" s="19"/>
       <c r="Z95" s="19"/>
     </row>
-    <row r="96" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A96" s="3" t="s">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A96" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
+      <c r="J96" s="19"/>
+      <c r="K96" s="19"/>
+      <c r="L96" s="19"/>
+      <c r="M96" s="19"/>
+      <c r="N96" s="19"/>
+      <c r="O96" s="19"/>
+      <c r="P96" s="19"/>
+      <c r="Q96" s="19"/>
+      <c r="R96" s="19"/>
+      <c r="S96" s="19"/>
+      <c r="T96" s="19"/>
+      <c r="U96" s="19"/>
+      <c r="V96" s="19"/>
+      <c r="W96" s="19"/>
+      <c r="X96" s="19"/>
+      <c r="Y96" s="19"/>
+      <c r="Z96" s="19"/>
+    </row>
+    <row r="97" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A97" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-    </row>
-    <row r="97" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -4914,23 +4941,13 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A98" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
-      <c r="G98" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
@@ -4951,24 +4968,24 @@
       <c r="Y98" s="4"/>
       <c r="Z98" s="4"/>
     </row>
-    <row r="99" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A99" s="3" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>56</v>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
@@ -4989,16 +5006,22 @@
       <c r="Y99" s="4"/>
       <c r="Z99" s="4"/>
     </row>
-    <row r="100" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A100" s="3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
+      <c r="C100" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -5022,8 +5045,12 @@
       <c r="Z100" s="4"/>
     </row>
     <row r="101" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
+      <c r="A101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -5050,23 +5077,13 @@
       <c r="Z101" s="4"/>
     </row>
     <row r="102" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A102" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
-      <c r="G102" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
@@ -5087,22 +5104,24 @@
       <c r="Y102" s="4"/>
       <c r="Z102" s="4"/>
     </row>
-    <row r="103" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A103" s="3" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
+      <c r="G103" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
@@ -5123,22 +5142,20 @@
       <c r="Y103" s="4"/>
       <c r="Z103" s="4"/>
     </row>
-    <row r="104" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A104" s="3" t="s">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -5161,25 +5178,23 @@
       <c r="Y104" s="4"/>
       <c r="Z104" s="4"/>
     </row>
-    <row r="105" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A105" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>174</v>
-      </c>
+      <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -5201,17 +5216,25 @@
       <c r="Y105" s="4"/>
       <c r="Z105" s="4"/>
     </row>
-    <row r="106" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A106" s="3" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
+      <c r="C106" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -5234,8 +5257,12 @@
       <c r="Z106" s="4"/>
     </row>
     <row r="107" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
+      <c r="A107" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -5262,23 +5289,13 @@
       <c r="Z107" s="4"/>
     </row>
     <row r="108" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A108" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
-      <c r="G108" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -5299,22 +5316,24 @@
       <c r="Y108" s="4"/>
       <c r="Z108" s="4"/>
     </row>
-    <row r="109" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A109" s="3" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
+      <c r="G109" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -5335,22 +5354,20 @@
       <c r="Y109" s="4"/>
       <c r="Z109" s="4"/>
     </row>
-    <row r="110" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A110" s="3" t="s">
-        <v>181</v>
+        <v>42</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -5378,18 +5395,18 @@
         <v>181</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F111" s="3"/>
+      <c r="F111" s="4"/>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -5411,18 +5428,18 @@
       <c r="Y111" s="4"/>
       <c r="Z111" s="4"/>
     </row>
-    <row r="112" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A112" s="3" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>56</v>
@@ -5449,17 +5466,23 @@
       <c r="Y112" s="4"/>
       <c r="Z112" s="4"/>
     </row>
-    <row r="113" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A113" s="3" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
+      <c r="C113" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F113" s="3"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -5482,8 +5505,12 @@
       <c r="Z113" s="4"/>
     </row>
     <row r="114" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
+      <c r="A114" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -5510,23 +5537,13 @@
       <c r="Z114" s="4"/>
     </row>
     <row r="115" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A115" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
-      <c r="G115" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
@@ -5549,22 +5566,22 @@
     </row>
     <row r="116" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A116" s="3" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>56</v>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -5585,20 +5602,22 @@
       <c r="Y116" s="4"/>
       <c r="Z116" s="4"/>
     </row>
-    <row r="117" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A117" s="3" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
-      <c r="E117" s="4"/>
+      <c r="E117" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -5621,15 +5640,19 @@
       <c r="Y117" s="4"/>
       <c r="Z117" s="4"/>
     </row>
-    <row r="118" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:26" ht="39" x14ac:dyDescent="0.6">
       <c r="A118" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
+      <c r="C118" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
@@ -5654,8 +5677,12 @@
       <c r="Z118" s="4"/>
     </row>
     <row r="119" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
+      <c r="A119" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -5681,55 +5708,45 @@
       <c r="Y119" s="4"/>
       <c r="Z119" s="4"/>
     </row>
-    <row r="120" spans="1:26" ht="143.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A120" s="5" t="s">
+    <row r="120" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="4"/>
+      <c r="T120" s="4"/>
+      <c r="U120" s="4"/>
+      <c r="V120" s="4"/>
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
+    </row>
+    <row r="121" spans="1:26" ht="143.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A121" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B121" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="L120" s="6"/>
-      <c r="M120" s="6"/>
-      <c r="N120" s="6"/>
-      <c r="O120" s="6"/>
-      <c r="P120" s="6"/>
-      <c r="Q120" s="6"/>
-      <c r="R120" s="6"/>
-      <c r="S120" s="6"/>
-      <c r="T120" s="6"/>
-      <c r="U120" s="6"/>
-      <c r="V120" s="6"/>
-      <c r="W120" s="6"/>
-      <c r="X120" s="6"/>
-      <c r="Y120" s="6"/>
-      <c r="Z120" s="6"/>
-    </row>
-    <row r="121" spans="1:26" ht="143.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A121" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="5" t="s">
         <v>201</v>
       </c>
       <c r="E121" s="6"/>
@@ -5738,8 +5755,8 @@
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
-      <c r="K121" s="6" t="s">
-        <v>326</v>
+      <c r="K121" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
@@ -5757,240 +5774,242 @@
       <c r="Y121" s="6"/>
       <c r="Z121" s="6"/>
     </row>
-    <row r="122" spans="1:26" ht="409.5" x14ac:dyDescent="0.6">
-      <c r="A122" s="7" t="s">
+    <row r="122" spans="1:26" ht="143.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A122" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="6"/>
+      <c r="O122" s="6"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="6"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="6"/>
+      <c r="T122" s="6"/>
+      <c r="U122" s="6"/>
+      <c r="V122" s="6"/>
+      <c r="W122" s="6"/>
+      <c r="X122" s="6"/>
+      <c r="Y122" s="6"/>
+      <c r="Z122" s="6"/>
+    </row>
+    <row r="123" spans="1:26" ht="409.5" x14ac:dyDescent="0.6">
+      <c r="A123" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C123" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D123" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="7" t="s">
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="L122" s="7"/>
-      <c r="M122" s="8"/>
-      <c r="N122" s="8"/>
-      <c r="O122" s="8"/>
-      <c r="P122" s="8"/>
-      <c r="Q122" s="8"/>
-      <c r="R122" s="8"/>
-      <c r="S122" s="8"/>
-      <c r="T122" s="8"/>
-      <c r="U122" s="8"/>
-      <c r="V122" s="8"/>
-      <c r="W122" s="8"/>
-      <c r="X122" s="8"/>
-      <c r="Y122" s="8"/>
-      <c r="Z122" s="8"/>
-    </row>
-    <row r="123" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
-      <c r="K123" s="3" t="s">
+      <c r="L123" s="7"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="8"/>
+      <c r="O123" s="8"/>
+      <c r="P123" s="8"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="8"/>
+      <c r="S123" s="8"/>
+      <c r="T123" s="8"/>
+      <c r="U123" s="8"/>
+      <c r="V123" s="8"/>
+      <c r="W123" s="8"/>
+      <c r="X123" s="8"/>
+      <c r="Y123" s="8"/>
+      <c r="Z123" s="8"/>
+    </row>
+    <row r="124" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4"/>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-      <c r="P123" s="4"/>
-      <c r="Q123" s="4"/>
-      <c r="R123" s="4"/>
-      <c r="S123" s="4"/>
-      <c r="T123" s="4"/>
-      <c r="U123" s="4"/>
-      <c r="V123" s="4"/>
-      <c r="W123" s="4"/>
-      <c r="X123" s="4"/>
-      <c r="Y123" s="4"/>
-      <c r="Z123" s="4"/>
-    </row>
-    <row r="124" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A124" s="9" t="s">
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="4"/>
+      <c r="T124" s="4"/>
+      <c r="U124" s="4"/>
+      <c r="V124" s="4"/>
+      <c r="W124" s="4"/>
+      <c r="X124" s="4"/>
+      <c r="Y124" s="4"/>
+      <c r="Z124" s="4"/>
+    </row>
+    <row r="125" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A125" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B125" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C125" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D125" s="10" t="s">
         <v>303</v>
-      </c>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10"/>
-      <c r="G124" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="H124" s="10"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
-      <c r="M124" s="10"/>
-      <c r="N124" s="10"/>
-      <c r="O124" s="10"/>
-      <c r="P124" s="10"/>
-      <c r="Q124" s="10"/>
-      <c r="R124" s="10"/>
-      <c r="S124" s="10"/>
-      <c r="T124" s="10"/>
-      <c r="U124" s="10"/>
-      <c r="V124" s="10"/>
-      <c r="W124" s="10"/>
-      <c r="X124" s="10"/>
-      <c r="Y124" s="10"/>
-      <c r="Z124" s="10"/>
-    </row>
-    <row r="125" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A125" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>304</v>
       </c>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="4"/>
-      <c r="K125" s="4"/>
-      <c r="L125" s="4"/>
-      <c r="M125" s="4"/>
-      <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
-      <c r="P125" s="4"/>
-      <c r="Q125" s="4"/>
-      <c r="R125" s="4"/>
-      <c r="S125" s="4"/>
-      <c r="T125" s="4"/>
-      <c r="U125" s="4"/>
-      <c r="V125" s="4"/>
-      <c r="W125" s="4"/>
-      <c r="X125" s="4"/>
-      <c r="Y125" s="4"/>
-      <c r="Z125" s="4"/>
+      <c r="H125" s="10"/>
+      <c r="I125" s="10"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="10"/>
+      <c r="L125" s="10"/>
+      <c r="M125" s="10"/>
+      <c r="N125" s="10"/>
+      <c r="O125" s="10"/>
+      <c r="P125" s="10"/>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="10"/>
+      <c r="S125" s="10"/>
+      <c r="T125" s="10"/>
+      <c r="U125" s="10"/>
+      <c r="V125" s="10"/>
+      <c r="W125" s="10"/>
+      <c r="X125" s="10"/>
+      <c r="Y125" s="10"/>
+      <c r="Z125" s="10"/>
     </row>
     <row r="126" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A126" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>336</v>
+        <v>208</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="10"/>
-      <c r="K126" s="10"/>
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
-      <c r="N126" s="10"/>
-      <c r="O126" s="10"/>
-      <c r="P126" s="10"/>
-      <c r="Q126" s="10"/>
-      <c r="R126" s="10"/>
-      <c r="S126" s="10"/>
-      <c r="T126" s="10"/>
-      <c r="U126" s="10"/>
-      <c r="V126" s="10"/>
-      <c r="W126" s="10"/>
-      <c r="X126" s="10"/>
-      <c r="Y126" s="10"/>
-      <c r="Z126" s="10"/>
+      <c r="G126" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4"/>
+      <c r="S126" s="4"/>
+      <c r="T126" s="4"/>
+      <c r="U126" s="4"/>
+      <c r="V126" s="4"/>
+      <c r="W126" s="4"/>
+      <c r="X126" s="4"/>
+      <c r="Y126" s="4"/>
+      <c r="Z126" s="4"/>
     </row>
     <row r="127" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>211</v>
+      <c r="B127" s="9" t="s">
+        <v>210</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>212</v>
+      <c r="C127" s="9" t="s">
+        <v>336</v>
       </c>
-      <c r="D127" s="4" t="s">
-        <v>305</v>
+      <c r="D127" s="13" t="s">
+        <v>337</v>
       </c>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
-      <c r="N127" s="4"/>
-      <c r="O127" s="4"/>
-      <c r="P127" s="4"/>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4"/>
-      <c r="S127" s="4"/>
-      <c r="T127" s="4"/>
-      <c r="U127" s="4"/>
-      <c r="V127" s="4"/>
-      <c r="W127" s="4"/>
-      <c r="X127" s="4"/>
-      <c r="Y127" s="4"/>
-      <c r="Z127" s="4"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
+      <c r="L127" s="10"/>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10"/>
+      <c r="O127" s="10"/>
+      <c r="P127" s="10"/>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="10"/>
+      <c r="S127" s="10"/>
+      <c r="T127" s="10"/>
+      <c r="U127" s="10"/>
+      <c r="V127" s="10"/>
+      <c r="W127" s="10"/>
+      <c r="X127" s="10"/>
+      <c r="Y127" s="10"/>
+      <c r="Z127" s="10"/>
     </row>
     <row r="128" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A128" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
+      <c r="G128" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
@@ -6012,61 +6031,59 @@
       <c r="Z128" s="4"/>
     </row>
     <row r="129" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B129" s="9" t="s">
+      <c r="B129" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4"/>
+      <c r="S129" s="4"/>
+      <c r="T129" s="4"/>
+      <c r="U129" s="4"/>
+      <c r="V129" s="4"/>
+      <c r="W129" s="4"/>
+      <c r="X129" s="4"/>
+      <c r="Y129" s="4"/>
+      <c r="Z129" s="4"/>
+    </row>
+    <row r="130" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A130" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B130" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C130" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D130" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="E129" s="10"/>
-      <c r="F129" s="10"/>
-      <c r="G129" s="11" t="s">
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
+      <c r="G130" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="H129" s="10"/>
-      <c r="I129" s="10"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="10"/>
-      <c r="L129" s="10"/>
-      <c r="M129" s="10"/>
-      <c r="N129" s="10"/>
-      <c r="O129" s="10"/>
-      <c r="P129" s="10"/>
-      <c r="Q129" s="10"/>
-      <c r="R129" s="10"/>
-      <c r="S129" s="10"/>
-      <c r="T129" s="10"/>
-      <c r="U129" s="10"/>
-      <c r="V129" s="10"/>
-      <c r="W129" s="10"/>
-      <c r="X129" s="10"/>
-      <c r="Y129" s="10"/>
-      <c r="Z129" s="10"/>
-    </row>
-    <row r="130" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A130" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E130" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F130" s="10"/>
-      <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10"/>
       <c r="J130" s="10"/>
@@ -6087,76 +6104,74 @@
       <c r="Y130" s="10"/>
       <c r="Z130" s="10"/>
     </row>
-    <row r="131" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A131" s="12" t="s">
+    <row r="131" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A131" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="10"/>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
+      <c r="T131" s="10"/>
+      <c r="U131" s="10"/>
+      <c r="V131" s="10"/>
+      <c r="W131" s="10"/>
+      <c r="X131" s="10"/>
+      <c r="Y131" s="10"/>
+      <c r="Z131" s="10"/>
+    </row>
+    <row r="132" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A132" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B132" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D132" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E132" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G131" s="4"/>
-      <c r="H131" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J131" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="K131" s="4"/>
-      <c r="L131" s="4"/>
-      <c r="M131" s="4"/>
-      <c r="N131" s="4"/>
-      <c r="O131" s="4"/>
-      <c r="P131" s="4"/>
-      <c r="Q131" s="4"/>
-      <c r="R131" s="4"/>
-      <c r="S131" s="4"/>
-      <c r="T131" s="4"/>
-      <c r="U131" s="4"/>
-      <c r="V131" s="4"/>
-      <c r="W131" s="4"/>
-      <c r="X131" s="4"/>
-      <c r="Y131" s="4"/>
-      <c r="Z131" s="4"/>
-    </row>
-    <row r="132" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A132" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E132" s="4"/>
       <c r="F132" s="3" t="s">
         <v>223</v>
       </c>
       <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="3" t="s">
-        <v>227</v>
+      <c r="H132" s="3" t="s">
+        <v>224</v>
       </c>
+      <c r="I132" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K132" s="4"/>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
@@ -6173,28 +6188,30 @@
       <c r="Y132" s="4"/>
       <c r="Z132" s="4"/>
     </row>
-    <row r="133" spans="1:26" ht="52" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A133" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>310</v>
+        <v>201</v>
       </c>
       <c r="E133" s="4"/>
-      <c r="F133" s="24" t="s">
-        <v>338</v>
+      <c r="F133" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
-      <c r="K133" s="4"/>
+      <c r="K133" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
@@ -6211,66 +6228,66 @@
       <c r="Y133" s="4"/>
       <c r="Z133" s="4"/>
     </row>
-    <row r="134" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A134" s="9" t="s">
+    <row r="134" spans="1:26" ht="52" x14ac:dyDescent="0.6">
+      <c r="A134" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4"/>
+      <c r="N134" s="4"/>
+      <c r="O134" s="4"/>
+      <c r="P134" s="4"/>
+      <c r="Q134" s="4"/>
+      <c r="R134" s="4"/>
+      <c r="S134" s="4"/>
+      <c r="T134" s="4"/>
+      <c r="U134" s="4"/>
+      <c r="V134" s="4"/>
+      <c r="W134" s="4"/>
+      <c r="X134" s="4"/>
+      <c r="Y134" s="4"/>
+      <c r="Z134" s="4"/>
+    </row>
+    <row r="135" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A135" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B135" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C135" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D135" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E134" s="10"/>
-      <c r="F134" s="10"/>
-      <c r="G134" s="10"/>
-      <c r="H134" s="10"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="10"/>
-      <c r="K134" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="L134" s="10"/>
-      <c r="M134" s="10"/>
-      <c r="N134" s="10"/>
-      <c r="O134" s="10"/>
-      <c r="P134" s="10"/>
-      <c r="Q134" s="10"/>
-      <c r="R134" s="10"/>
-      <c r="S134" s="10"/>
-      <c r="T134" s="10"/>
-      <c r="U134" s="10"/>
-      <c r="V134" s="10"/>
-      <c r="W134" s="10"/>
-      <c r="X134" s="10"/>
-      <c r="Y134" s="10"/>
-      <c r="Z134" s="10"/>
-    </row>
-    <row r="135" spans="1:26" ht="52" x14ac:dyDescent="0.6">
-      <c r="A135" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C135" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>311</v>
-      </c>
       <c r="E135" s="10"/>
-      <c r="F135" s="25" t="s">
-        <v>338</v>
-      </c>
+      <c r="F135" s="10"/>
       <c r="G135" s="10"/>
       <c r="H135" s="10"/>
       <c r="I135" s="10"/>
       <c r="J135" s="10"/>
-      <c r="K135" s="10"/>
+      <c r="K135" s="13" t="s">
+        <v>231</v>
+      </c>
       <c r="L135" s="10"/>
       <c r="M135" s="10"/>
       <c r="N135" s="10"/>
@@ -6287,17 +6304,23 @@
       <c r="Y135" s="10"/>
       <c r="Z135" s="10"/>
     </row>
-    <row r="136" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:26" ht="52" x14ac:dyDescent="0.6">
       <c r="A136" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
-      <c r="C136" s="10"/>
-      <c r="D136" s="10"/>
+      <c r="C136" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>311</v>
+      </c>
       <c r="E136" s="10"/>
-      <c r="F136" s="10"/>
+      <c r="F136" s="25" t="s">
+        <v>338</v>
+      </c>
       <c r="G136" s="10"/>
       <c r="H136" s="10"/>
       <c r="I136" s="10"/>
@@ -6320,32 +6343,36 @@
       <c r="Z136" s="10"/>
     </row>
     <row r="137" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
-      <c r="V137" s="4"/>
-      <c r="W137" s="4"/>
-      <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
+      <c r="A137" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C137" s="10"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
+      <c r="G137" s="10"/>
+      <c r="H137" s="10"/>
+      <c r="I137" s="10"/>
+      <c r="J137" s="10"/>
+      <c r="K137" s="10"/>
+      <c r="L137" s="10"/>
+      <c r="M137" s="10"/>
+      <c r="N137" s="10"/>
+      <c r="O137" s="10"/>
+      <c r="P137" s="10"/>
+      <c r="Q137" s="10"/>
+      <c r="R137" s="10"/>
+      <c r="S137" s="10"/>
+      <c r="T137" s="10"/>
+      <c r="U137" s="10"/>
+      <c r="V137" s="10"/>
+      <c r="W137" s="10"/>
+      <c r="X137" s="10"/>
+      <c r="Y137" s="10"/>
+      <c r="Z137" s="10"/>
     </row>
     <row r="138" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A138" s="4"/>
@@ -30398,6 +30425,34 @@
       <c r="X996" s="4"/>
       <c r="Y996" s="4"/>
       <c r="Z996" s="4"/>
+    </row>
+    <row r="997" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A997" s="4"/>
+      <c r="B997" s="4"/>
+      <c r="C997" s="4"/>
+      <c r="D997" s="4"/>
+      <c r="E997" s="4"/>
+      <c r="F997" s="4"/>
+      <c r="G997" s="4"/>
+      <c r="H997" s="4"/>
+      <c r="I997" s="4"/>
+      <c r="J997" s="4"/>
+      <c r="K997" s="4"/>
+      <c r="L997" s="4"/>
+      <c r="M997" s="4"/>
+      <c r="N997" s="4"/>
+      <c r="O997" s="4"/>
+      <c r="P997" s="4"/>
+      <c r="Q997" s="4"/>
+      <c r="R997" s="4"/>
+      <c r="S997" s="4"/>
+      <c r="T997" s="4"/>
+      <c r="U997" s="4"/>
+      <c r="V997" s="4"/>
+      <c r="W997" s="4"/>
+      <c r="X997" s="4"/>
+      <c r="Y997" s="4"/>
+      <c r="Z997" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30685,7 +30740,7 @@
       </c>
       <c r="C2" s="17">
         <f ca="1">NOW()</f>
-        <v>44825.55971076389</v>
+        <v>44902.450267129629</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>268</v>
